--- a/test/generator/baseline/gen.csv.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.csv.to.xlsx.xlsx
@@ -12,9 +12,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -46,12 +43,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -555,8 +551,10 @@
       <c r="C59">
         <v>103</v>
       </c>
-      <c r="D59">
-        <v>7</v>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+7 </t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -594,8 +592,10 @@
       <c r="C62">
         <v>20</v>
       </c>
-      <c r="D62">
-        <v>4</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+4 </t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -1178,10 +1178,10 @@
           <t xml:space="preserve">Category 1</t>
         </is>
       </c>
-      <c r="B136" s="2">
+      <c r="B136">
         <v>4.3</v>
       </c>
-      <c r="C136" s="2">
+      <c r="C136">
         <v>2.4</v>
       </c>
       <c r="D136">
@@ -1194,13 +1194,11 @@
           <t xml:space="preserve">Category 2</t>
         </is>
       </c>
-      <c r="B137" s="2">
+      <c r="B137">
         <v>2.5</v>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.4000000000000004</t>
-        </is>
+      <c r="C137">
+        <v>4.4</v>
       </c>
       <c r="D137">
         <v>2</v>
@@ -1212,10 +1210,10 @@
           <t xml:space="preserve">Category 3</t>
         </is>
       </c>
-      <c r="B138" s="2">
+      <c r="B138">
         <v>3.5</v>
       </c>
-      <c r="C138" s="2">
+      <c r="C138">
         <v>1.8</v>
       </c>
       <c r="D138">
@@ -1228,10 +1226,10 @@
           <t xml:space="preserve">Category 4</t>
         </is>
       </c>
-      <c r="B139" s="2">
+      <c r="B139">
         <v>4.5</v>
       </c>
-      <c r="C139" s="2">
+      <c r="C139">
         <v>2.8</v>
       </c>
       <c r="D139">

--- a/test/generator/baseline/gen.csv.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.csv.to.xlsx.xlsx
@@ -6,6 +6,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Notes" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -1238,4 +1239,159 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comment</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># TestString: Hello from custom props</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># TestNumber: 42</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comment</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># TestBool: true</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comment</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sheet: Sheet1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comment</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sheet: Sheet2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comment</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sheet: Sheet3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comment</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sheet: Sheet4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comment</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sheet: Sheet5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comment</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sheet: Sheet6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comment</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sheet: Sheet7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comment</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sheet: Sheet8</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comment</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sheet: Chart Sheet</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/test/generator/baseline/gen.csv.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.csv.to.xlsx.xlsx
@@ -13,6 +13,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -44,11 +47,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1179,10 +1183,10 @@
           <t xml:space="preserve">Category 1</t>
         </is>
       </c>
-      <c r="B136">
+      <c r="B136" s="2">
         <v>4.3</v>
       </c>
-      <c r="C136">
+      <c r="C136" s="2">
         <v>2.4</v>
       </c>
       <c r="D136">
@@ -1195,11 +1199,13 @@
           <t xml:space="preserve">Category 2</t>
         </is>
       </c>
-      <c r="B137">
+      <c r="B137" s="2">
         <v>2.5</v>
       </c>
-      <c r="C137">
-        <v>4.4</v>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4000000000000004</t>
+        </is>
       </c>
       <c r="D137">
         <v>2</v>
@@ -1211,10 +1217,10 @@
           <t xml:space="preserve">Category 3</t>
         </is>
       </c>
-      <c r="B138">
+      <c r="B138" s="2">
         <v>3.5</v>
       </c>
-      <c r="C138">
+      <c r="C138" s="2">
         <v>1.8</v>
       </c>
       <c r="D138">
@@ -1227,10 +1233,10 @@
           <t xml:space="preserve">Category 4</t>
         </is>
       </c>
-      <c r="B139">
+      <c r="B139" s="2">
         <v>4.5</v>
       </c>
-      <c r="C139">
+      <c r="C139" s="2">
         <v>2.8</v>
       </c>
       <c r="D139">

--- a/test/generator/baseline/gen.csv.to.xlsx.xlsx
+++ b/test/generator/baseline/gen.csv.to.xlsx.xlsx
@@ -6,7 +6,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Notes" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -70,11 +69,8 @@
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
     <col min="9" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="8" customWidth="1"/>
-    <col min="12" max="12" width="8" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
   </cols>
   <sheetData>
@@ -102,6 +98,34 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># TestString: Hello from custom props</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># TestNumber: 42</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># TestBool: true</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sheet: Sheet1</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -214,6 +238,13 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sheet: Sheet2</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -299,6 +330,13 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sheet: Sheet3</t>
+        </is>
+      </c>
+    </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
@@ -508,6 +546,13 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sheet: Sheet4</t>
+        </is>
+      </c>
+    </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
@@ -677,6 +722,13 @@
       <c r="A69" t="inlineStr">
         <is>
           <t xml:space="preserve">Four </t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sheet: Sheet5</t>
         </is>
       </c>
     </row>
@@ -836,6 +888,13 @@
         <v>31</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sheet: Sheet6</t>
+        </is>
+      </c>
+    </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -899,6 +958,13 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sheet: Sheet7</t>
+        </is>
+      </c>
+    </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
@@ -917,6 +983,13 @@
       <c r="A102" t="inlineStr">
         <is>
           <t xml:space="preserve">There is no analogous technology in ebooks, so the conversion will usually end up placing the image either centered or floating close to the point in the text where it was inserted, not necessarily where it appears on the page in Word. </t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sheet: Sheet8</t>
         </is>
       </c>
     </row>
@@ -1153,6 +1226,13 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sheet: Chart Sheet</t>
+        </is>
+      </c>
+    </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
@@ -1241,161 +1321,6 @@
       </c>
       <c r="D139">
         <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comment</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># TestString: Hello from custom props</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comment</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># TestNumber: 42</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comment</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># TestBool: true</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comment</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># Sheet: Sheet1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comment</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># Sheet: Sheet2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comment</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># Sheet: Sheet3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comment</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># Sheet: Sheet4</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comment</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># Sheet: Sheet5</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comment</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># Sheet: Sheet6</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comment</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># Sheet: Sheet7</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comment</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># Sheet: Sheet8</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comment</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># Sheet: Chart Sheet</t>
-        </is>
       </c>
     </row>
   </sheetData>
